--- a/stories/arbres/ATOM-SEC.MAI.003-01.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.003-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Inès est à la maison. Maman ouvre la porte du balcon. L'air sent les fleurs. Inès reste avec l'adulte. Maman dit : on reste derrière la protection. Inès pose les pieds au sol. Les pieds restent au sol. Elle sent le bois sous les chaussettes. La protection est devant elle. Inès pose les mains sur la protection. Elle reste derrière la protection. Un oiseau passe. Inès dit : maman, l'oiseau. Maman est près d'elle. Parce que les pieds sont au sol, Inès est calme. L'adulte regarde le ciel avec elle. Elles respirent. C'est doux.</t>
+          <t>Inès est à la maison. Maman ouvre la porte du balcon. L'air sent les fleurs. Inès reste avec l'adulte. On reste derrière la protection. Inès pose les pieds au sol. Les pieds restent au sol. Elle sent le bois sous les chaussettes. La protection est devant elle. Inès pose les mains sur la protection. Elle reste derrière la protection. Un oiseau passe. Maman, l'oiseau. Maman est près d'elle. Parce que les pieds sont au sol, Inès est calme. L'adulte regarde le ciel avec elle. Elles respirent. C'est doux.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,14 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Inès est à la maison. Maman ouvre la porte du balcon. L'air sent les fleurs. Inès reste avec l'adulte.
+maman|On reste derrière la protection.
+narrateur|Inès pose les pieds au sol. Les pieds restent au sol. Elle sent le bois sous les chaussettes. La protection est devant elle. Inès pose les mains sur la protection. Elle reste derrière la protection. Un oiseau passe.
+enfant-f|Maman, l'oiseau. Maman est près d'elle. Parce que les pieds sont au sol, Inès est calme. L'adulte regarde le ciel avec elle. Elles respirent. C'est doux.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1493,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Inès est au balcon. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1670,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a les pieds au sol. Elle est derrière la protection. Maman est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1807,6 +1841,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Inès et maman rentrent. Les pieds restent au sol.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,6 +2008,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1987,7 +2031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2004,6 +2048,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.003-01.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.003-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1313,6 +1318,11 @@
 enfant-f|Maman, l'oiseau. Maman est près d'elle. Parce que les pieds sont au sol, Inès est calme. L'adulte regarde le ciel avec elle. Elles respirent. C'est doux.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1500,6 +1510,7 @@
           <t>narrateur|Inès est au balcon. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1675,6 +1686,7 @@
           <t>narrateur|Inès a les pieds au sol. Elle est derrière la protection. Maman est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1846,6 +1858,7 @@
           <t>narrateur|Inès et maman rentrent. Les pieds restent au sol.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2013,6 +2026,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2031,7 +2045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2055,6 +2069,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2256,6 +2284,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.MAI.003-01.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.003-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Inès au balcon</t>
+          <t>Le rideau de Mila</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le rideau blanc respire. Mila va au balcon avec maman. Pieds au sol, derrière la protection. Un oiseau passe. Elles rentrent.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Inès est à la maison. Maman ouvre la porte du balcon. L'air sent les fleurs. Inès reste avec l'adulte. On reste derrière la protection. Inès pose les pieds au sol. Les pieds restent au sol. Elle sent le bois sous les chaussettes. La protection est devant elle. Inès pose les mains sur la protection. Elle reste derrière la protection. Un oiseau passe. Maman, l'oiseau. Maman est près d'elle. Parce que les pieds sont au sol, Inès est calme. L'adulte regarde le ciel avec elle. Elles respirent. C'est doux.</t>
+          <t>Le rideau blanc respire, tout doucement. Il va, puis il revient. Un rayon chaud touche le plancher. Le bois est lisse sous les chaussettes. Ça sent les fleurs, près de la porte. Un pot rose attend sur le rebord. Une abeille passe, tout loin. Le bois de la porte est chaud. Tu as vu le rideau, Mila ? Oui, maman. Il danse un peu. L'air est doux, aujourd'hui. En ce moment, maman ouvre la porte. L'air sent les fleurs, plus fort. Mila reste avec l'adulte. On reste derrière la protection. D'accord, maman. Mila pose les pieds au sol. Les pieds restent au sol. Elle sent le bois sous les chaussettes. La protection est devant elle. Mila pose les mains sur la protection. Elle reste derrière la protection. Bravo, Mila. Tes pieds sont au sol. Un oiseau passe, tout léger. Maman, l'oiseau. Je le vois. On le regarde ici, avec moi. Maman est près d'elle. Parce que les pieds sont au sol, Mila est calme. L'adulte regarde le ciel avec elle. Tu entends l'oiseau ? Oui. Il chante. On reste avec l'adulte. Derrière la protection. Pieds au sol. Oui. C'est du bon travail. Elles respirent. C'est doux. Tu as fini de regarder l'oiseau ? Encore un peu. Encore un peu, d'accord. Le pot rose ne bouge pas. Les pieds restent au sol. Tu sens le bois, sous tes pieds ? Oui. Il est chaud. On reste derrière la protection.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,15 +1324,62 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Inès est à la maison. Maman ouvre la porte du balcon. L'air sent les fleurs. Inès reste avec l'adulte.
+          <t>narrateur|Le rideau blanc respire, tout doucement.
+narrateur|Il va, puis il revient.
+narrateur|Un rayon chaud touche le plancher.
+narrateur|Le bois est lisse sous les chaussettes.
+narrateur|Ça sent les fleurs, près de la porte.
+narrateur|Un pot rose attend sur le rebord.
+narrateur|Une abeille passe, tout loin.
+narrateur|Le bois de la porte est chaud.
+maman|Tu as vu le rideau, Mila ?
+enfant-f|Oui, maman.
+enfant-f|Il danse un peu.
+maman|L'air est doux, aujourd'hui.
+narrateur|En ce moment, maman ouvre la porte.
+narrateur|L'air sent les fleurs, plus fort.
+narrateur|Mila reste avec l'adulte.
 maman|On reste derrière la protection.
-narrateur|Inès pose les pieds au sol. Les pieds restent au sol. Elle sent le bois sous les chaussettes. La protection est devant elle. Inès pose les mains sur la protection. Elle reste derrière la protection. Un oiseau passe.
-enfant-f|Maman, l'oiseau. Maman est près d'elle. Parce que les pieds sont au sol, Inès est calme. L'adulte regarde le ciel avec elle. Elles respirent. C'est doux.</t>
+enfant-f|D'accord, maman.
+narrateur|Mila pose les pieds au sol.
+narrateur|Les pieds restent au sol.
+narrateur|Elle sent le bois sous les chaussettes.
+narrateur|La protection est devant elle.
+narrateur|Mila pose les mains sur la protection.
+narrateur|Elle reste derrière la protection.
+maman|Bravo, Mila.
+maman|Tes pieds sont au sol.
+narrateur|Un oiseau passe, tout léger.
+enfant-f|Maman, l'oiseau.
+maman|Je le vois.
+maman|On le regarde ici, avec moi.
+narrateur|Maman est près d'elle.
+narrateur|Parce que les pieds sont au sol, Mila est calme.
+narrateur|L'adulte regarde le ciel avec elle.
+maman|Tu entends l'oiseau ?
+enfant-f|Oui.
+enfant-f|Il chante.
+maman|On reste avec l'adulte.
+maman|Derrière la protection.
+enfant-f|Pieds au sol.
+maman|Oui.
+maman|C'est du bon travail.
+narrateur|Elles respirent.
+narrateur|C'est doux.
+maman|Tu as fini de regarder l'oiseau ?
+enfant-f|Encore un peu.
+maman|Encore un peu, d'accord.
+narrateur|Le pot rose ne bouge pas.
+narrateur|Les pieds restent au sol.
+maman|Tu sens le bois, sous tes pieds ?
+enfant-f|Oui.
+enfant-f|Il est chaud.
+maman|On reste derrière la protection.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>oiseau,rideau</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1406,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Inès est au balcon. Que fait-elle ?</t>
+          <t>Mila est au balcon. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1507,7 +1566,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Inès est au balcon. Que fait-elle ?</t>
+          <t>narrateur|Mila est au balcon.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1535,7 +1595,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Inès a les pieds au sol. Elle est derrière la protection. Maman est là.</t>
+          <t>Mila a les pieds au sol. Elle est derrière la protection. Tu es avec l'adulte. Bravo, Mila. Pieds au sol. Avec maman. Oui. C'est du bon travail. Tu restes derrière la protection ? Oui, maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1683,7 +1743,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Inès a les pieds au sol. Elle est derrière la protection. Maman est là.</t>
+          <t>narrateur|Mila a les pieds au sol.
+narrateur|Elle est derrière la protection.
+maman|Tu es avec l'adulte.
+maman|Bravo, Mila.
+enfant-f|Pieds au sol.
+enfant-f|Avec maman.
+maman|Oui.
+maman|C'est du bon travail.
+maman|Tu restes derrière la protection ?
+enfant-f|Oui, maman.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1711,7 +1780,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Inès et maman rentrent. Les pieds restent au sol.</t>
+          <t>Mila et maman rentrent. Les pieds restent au sol. Le rideau blanc respire encore. On ferme la porte, tout doux ? Oui. La porte fait un petit clic. Le tapis est doux sous les chaussettes. Tu as les pieds au sol, encore. Bravo. L'oiseau est parti. On l'a regardé ensemble. Derrière la protection. Tu veux un peu d'eau ? Oui, maman. L'eau est fraîche. On était avec l'adulte.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1855,7 +1924,22 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Inès et maman rentrent. Les pieds restent au sol.</t>
+          <t>narrateur|Mila et maman rentrent.
+narrateur|Les pieds restent au sol.
+narrateur|Le rideau blanc respire encore.
+maman|On ferme la porte, tout doux ?
+enfant-f|Oui.
+narrateur|La porte fait un petit clic.
+narrateur|Le tapis est doux sous les chaussettes.
+maman|Tu as les pieds au sol, encore.
+maman|Bravo.
+enfant-f|L'oiseau est parti.
+maman|On l'a regardé ensemble.
+maman|Derrière la protection.
+maman|Tu veux un peu d'eau ?
+enfant-f|Oui, maman.
+narrateur|L'eau est fraîche.
+maman|On était avec l'adulte.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1883,7 +1967,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'avais les pieds au sol. Avec maman. Bravo. Tu as fait du bon travail. Le rideau redevient calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2023,7 +2107,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'avais les pieds au sol.
+enfant-f|Avec maman.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Le rideau redevient calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2045,7 +2134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2083,6 +2172,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.003-01.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.003-01.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le rideau blanc respire, tout doucement. Il va, puis il revient. Un rayon chaud touche le plancher. Le bois est lisse sous les chaussettes. Ça sent les fleurs, près de la porte. Un pot rose attend sur le rebord. Une abeille passe, tout loin. Le bois de la porte est chaud. Tu as vu le rideau, Mila ? Oui, maman. Il danse un peu. L'air est doux, aujourd'hui. En ce moment, maman ouvre la porte. L'air sent les fleurs, plus fort. Mila reste avec l'adulte. On reste derrière la protection. D'accord, maman. Mila pose les pieds au sol. Les pieds restent au sol. Elle sent le bois sous les chaussettes. La protection est devant elle. Mila pose les mains sur la protection. Elle reste derrière la protection. Bravo, Mila. Tes pieds sont au sol. Un oiseau passe, tout léger. Maman, l'oiseau. Je le vois. On le regarde ici, avec moi. Maman est près d'elle. Parce que les pieds sont au sol, Mila est calme. L'adulte regarde le ciel avec elle. Tu entends l'oiseau ? Oui. Il chante. On reste avec l'adulte. Derrière la protection. Pieds au sol. Oui. C'est du bon travail. Elles respirent. C'est doux. Tu as fini de regarder l'oiseau ? Encore un peu. Encore un peu, d'accord. Le pot rose ne bouge pas. Les pieds restent au sol. Tu sens le bois, sous tes pieds ? Oui. Il est chaud. On reste derrière la protection.</t>
+          <t>Le rideau blanc respire, tout doucement. Il va, puis il revient. Un rayon chaud touche le plancher. Le bois est lisse sous les chaussettes. Ça sent les fleurs, près de la porte. Un pot rose attend sur le rebord. Une abeille passe, tout loin. Le bois de la porte est chaud. Tu as vu le rideau, Mila ? Oui, maman. Il danse un peu. L'air est doux, aujourd'hui. En ce moment, maman ouvre la porte. L'air sent les fleurs, plus fort. Mila reste avec l'adulte. On reste derrière la protection. D'accord, maman. Mila pose les pieds au sol. Les pieds restent au sol. Elle sent le bois sous les chaussettes. La protection est devant elle. Mila pose les mains sur la protection. Elle reste derrière la protection. Bravo, Mila. Tes pieds sont au sol. Un oiseau passe, tout léger. Maman, l'oiseau. Je le vois. On le regarde ici, avec moi. Maman est près d'elle. Parce que les pieds sont au sol, Mila est calme. L'adulte regarde le ciel avec elle. Tu entends l'oiseau ? Oui. Il chante. On reste avec l'adulte. Derrière la protection. Pieds au sol. Oui. Elles respirent. C'est doux. Tu as fini de regarder l'oiseau ? Encore un peu. Encore un peu, d'accord. Le pot rose ne bouge pas. Les pieds restent au sol. Tu sens le bois, sous tes pieds ? Oui. Il est chaud. On reste derrière la protection.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Inès est à la maison. Maman ouvre la porte du balcon. L'air sent les fleurs. Inès reste avec l'adulte. Maman dit : on reste derrière la protection. Inès pose les &lt;emphasis level="moderate"&gt;pieds&lt;/emphasis&gt; au sol. Les pieds restent au sol. Elle sent le bois sous les chaussettes. La protection est devant elle. Inès pose les mains sur la protection. Elle reste derrière la protection. Un oiseau passe. Inès dit : maman, l'oiseau. Maman est près d'elle. Parce que les pieds sont au sol, Inès est calme. L'adulte regarde le ciel avec elle. Elles respirent. C'est doux.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le rideau blanc respire, tout doucement. Il va, puis il revient. Un rayon chaud touche le plancher. Le bois est lisse sous les chaussettes. Ça sent les fleurs, près de la porte. Un pot rose attend sur le rebord. Une abeille passe, tout loin. Le bois de la porte est chaud. Tu as vu le rideau, Mila ? Oui, maman. Il danse un peu. L'air est doux, aujourd'hui. En ce moment, maman ouvre la porte. L'air sent les fleurs, plus fort. Mila reste avec l'adulte. On reste derrière la protection. D'accord, maman. Mila pose les pieds au sol. Les pieds restent au sol. Elle sent le bois sous les chaussettes. La protection est devant elle. Mila pose les mains sur la protection. Elle reste derrière la protection. Bravo, Mila. Tes pieds sont au sol. Un oiseau passe, tout léger. Maman, l'oiseau. Je le vois. On le regarde ici, avec moi. Maman est près d'elle. Parce que les pieds sont au sol, Mila est calme. L'adulte regarde le ciel avec elle. Tu entends l'oiseau ? Oui. Il chante. On reste avec l'adulte. Derrière la protection. Pieds au sol. Oui. Elles respirent. C'est doux. Tu as fini de regarder l'oiseau ? Encore un peu. Encore un peu, d'accord. Le pot rose ne bouge pas. Les pieds restent au sol. Tu sens le bois, sous tes pieds ? Oui. Il est chaud. On reste derrière la protection.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1363,7 +1363,6 @@
 maman|Derrière la protection.
 enfant-f|Pieds au sol.
 maman|Oui.
-maman|C'est du bon travail.
 narrateur|Elles respirent.
 narrateur|C'est doux.
 maman|Tu as fini de regarder l'oiseau ?
@@ -1411,7 +1410,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Inès est au balcon. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila est au balcon. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1570,7 +1569,6 @@
 narrateur|Que fait-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1595,12 +1593,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Mila a les pieds au sol. Elle est derrière la protection. Tu es avec l'adulte. Bravo, Mila. Pieds au sol. Avec maman. Oui. C'est du bon travail. Tu restes derrière la protection ? Oui, maman.</t>
+          <t>Mila a les pieds au sol. Elle est derrière la protection. Tu es avec l'adulte. Bravo, Mila. Pieds au sol. Avec maman. Oui. Tu restes derrière la protection ? Oui, maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Inès a les &lt;emphasis level="moderate"&gt;pieds&lt;/emphasis&gt; au sol. Elle est derrière la protection. Maman est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila a les pieds au sol. Elle est derrière la protection. Tu es avec l'adulte. Bravo, Mila. Pieds au sol. Avec maman. Oui. Tu restes derrière la protection ? Oui, maman.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1750,12 +1748,10 @@
 enfant-f|Pieds au sol.
 enfant-f|Avec maman.
 maman|Oui.
-maman|C'est du bon travail.
 maman|Tu restes derrière la protection ?
 enfant-f|Oui, maman.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1785,7 +1781,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Inès et maman rentrent. Les &lt;emphasis level="moderate"&gt;pieds&lt;/emphasis&gt; restent au sol.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila et maman rentrent. Les pieds restent au sol. Le rideau blanc respire encore. On ferme la porte, tout doux ? Oui. La porte fait un petit clic. Le tapis est doux sous les chaussettes. Tu as les pieds au sol, encore. Bravo. L'oiseau est parti. On l'a regardé ensemble. Derrière la protection. Tu veux un peu d'eau ? Oui, maman. L'eau est fraîche. On était avec l'adulte.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1942,7 +1938,6 @@
 maman|On était avec l'adulte.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1967,12 +1962,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'avais les pieds au sol. Avec maman. Bravo. Tu as fait du bon travail. Le rideau redevient calme. L'histoire est finie.</t>
+          <t>J'avais les pieds au sol. Avec maman. Bravo. Le rideau redevient calme.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'avais les pieds au sol. Avec maman. Bravo. Le rideau redevient calme.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2110,12 +2105,9 @@
           <t>enfant-f|J'avais les pieds au sol.
 enfant-f|Avec maman.
 maman|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|Le rideau redevient calme.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le rideau redevient calme.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2134,7 +2126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2179,6 +2171,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.003-01.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.003-01.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Inès, maman</t>
+          <t>Mila, maman</t>
         </is>
       </c>
     </row>
